--- a/contact_forms/019_travel_contact_form--contact_forms.xlsx
+++ b/contact_forms/019_travel_contact_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'name':_'air',_'label':_'air',_'value':_'air',_'required':_true}</t>
+          <t>air</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'name': 'Air', 'label': 'Air', 'value': 'Air', 'required': True}</t>
+          <t>Air</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'name':_'train',_'label':_'train',_'value':_'train',_'required':_false}</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'name': 'Train', 'label': 'Train', 'value': 'Train', 'required': False}</t>
+          <t>Train</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'name':_'bus',_'label':_'bus',_'value':_'bus',_'required':_false}</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'name': 'Bus', 'label': 'Bus', 'value': 'Bus', 'required': False}</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'name':_'hotel',_'label':_'hotel',_'value':_'hotel',_'required':_true}</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'name': 'Hotel', 'label': 'Hotel', 'value': 'Hotel', 'required': True}</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'name':_'resort',_'label':_'resort',_'value':_'resort',_'required':_false}</t>
+          <t>resort</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'name': 'Resort', 'label': 'Resort', 'value': 'Resort', 'required': False}</t>
+          <t>Resort</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'name':_'hostel',_'label':_'hostel',_'value':_'hostel',_'required':_false}</t>
+          <t>hostel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'name': 'Hostel', 'label': 'Hostel', 'value': 'Hostel', 'required': False}</t>
+          <t>Hostel</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'name':_true,_'label':_true,_'value':_true,_'required':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'name': True, 'label': True, 'value': True, 'required': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'name':_false,_'label':_false,_'value':_false,_'required':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'name': False, 'label': False, 'value': False, 'required': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
